--- a/technicalaudittoolPRD_v2_source_register.xlsx
+++ b/technicalaudittoolPRD_v2_source_register.xlsx
@@ -10041,107 +10041,118 @@
         <v>52</v>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" s="5" t="s">
-        <v>60</v>
-      </c>
-      <c r="B13" s="7" t="s">
-        <v>133</v>
-      </c>
-      <c r="C13" s="5" t="s">
-        <v>135</v>
-      </c>
-      <c r="D13" s="7" t="s">
-        <v>55</v>
-      </c>
-      <c r="E13" s="7" t="s">
-        <v>66</v>
-      </c>
-      <c r="F13" s="5" t="s">
-        <v>137</v>
-      </c>
-      <c r="G13" s="7" t="s">
-        <v>119</v>
-      </c>
-      <c r="H13" s="9" t="s">
-        <v>68</v>
-      </c>
-      <c r="I13" s="11" t="s">
-        <v>28</v>
-      </c>
-      <c r="J13" s="7"/>
-      <c r="K13" s="5" t="s">
-        <v>148</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="5" t="s">
-        <v>60</v>
-      </c>
-      <c r="B14" s="7" t="s">
-        <v>149</v>
-      </c>
-      <c r="C14" s="5" t="s">
-        <v>150</v>
-      </c>
-      <c r="D14" s="7" t="s">
-        <v>55</v>
-      </c>
-      <c r="E14" s="7" t="s">
-        <v>66</v>
-      </c>
-      <c r="F14" s="5" t="s">
-        <v>151</v>
-      </c>
-      <c r="G14" s="7" t="s">
-        <v>152</v>
-      </c>
-      <c r="H14" s="9" t="s">
-        <v>68</v>
-      </c>
-      <c r="I14" s="11" t="s">
-        <v>28</v>
-      </c>
-      <c r="J14" s="12" t="s">
-        <v>69</v>
-      </c>
-      <c r="K14" s="5" t="s">
-        <v>153</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="5" t="s">
-        <v>60</v>
-      </c>
-      <c r="B15" s="7" t="s">
-        <v>154</v>
-      </c>
-      <c r="C15" s="5" t="s">
-        <v>155</v>
-      </c>
-      <c r="D15" s="7" t="s">
-        <v>55</v>
-      </c>
-      <c r="E15" s="7" t="s">
-        <v>104</v>
-      </c>
-      <c r="F15" s="5" t="s">
-        <v>156</v>
-      </c>
-      <c r="G15" s="7" t="s">
-        <v>157</v>
-      </c>
-      <c r="H15" s="5" t="s">
-        <v>158</v>
-      </c>
-      <c r="I15" s="20" t="s">
-        <v>106</v>
-      </c>
-      <c r="J15" s="12" t="s">
-        <v>69</v>
-      </c>
-      <c r="K15" s="5" t="s">
-        <v>163</v>
+    <row r="13" ht="15.75" customHeight="1">
+      <c r="A13" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">C-1.2</t>
+        </is>
+      </c>
+      <c r="B13" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">C-1.2-b</t>
+        </is>
+      </c>
+      <c r="C13" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">No parent sitemap located: robots.txt declares none, no standard location returns 200, and no request was inconclusive</t>
+        </is>
+      </c>
+      <c r="D13" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WARN</t>
+        </is>
+      </c>
+      <c r="E13" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LOW</t>
+        </is>
+      </c>
+      <c r="F13" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">SITEMAP_NOT_FOUND</t>
+        </is>
+      </c>
+      <c r="G13" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">G5</t>
+        </is>
+      </c>
+      <c r="H13" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://developers.google.com/search/docs/crawling-indexing/sitemaps/build-sitemap</t>
+        </is>
+      </c>
+      <c r="I13" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Google — documented</t>
+        </is>
+      </c>
+      <c r="J13" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Tool policy</t>
+        </is>
+      </c>
+      <c r="K13" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Google documents the Sitemap: directive and the standard locations, and states that a sitemap is not required for every site. Absence is therefore reported, not failed. The WARN/LOW grading is tool policy.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="15.75" customHeight="1">
+      <c r="A14" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">C-1.2</t>
+        </is>
+      </c>
+      <c r="B14" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">C-1.2-c</t>
+        </is>
+      </c>
+      <c r="C14" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">robots.txt declares a sitemap, every variant of it returns 4xx/5xx or a network failure, and no other declared or standard-location parent sitemap returns 200</t>
+        </is>
+      </c>
+      <c r="D14" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">FAIL</t>
+        </is>
+      </c>
+      <c r="E14" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">HIGH</t>
+        </is>
+      </c>
+      <c r="F14" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DECLARED_SITEMAP_UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="G14" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">G5, G2</t>
+        </is>
+      </c>
+      <c r="H14" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://developers.google.com/search/docs/crawling-indexing/sitemaps/build-sitemap</t>
+        </is>
+      </c>
+      <c r="I14" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Google — documented</t>
+        </is>
+      </c>
+      <c r="J14" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Tool policy</t>
+        </is>
+      </c>
+      <c r="K14" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">A URL the site advertises to crawlers in robots.txt, which does not resolve and has no working alternative, is a broken declaration. Both conditions are required: a dead declaration alongside a sitemap that does serve is C-1.2-j, not a failure.</t>
+        </is>
       </c>
     </row>
     <row r="16">
@@ -10177,41 +10188,6 @@
         <v>171</v>
       </c>
     </row>
-    <row r="17">
-      <c r="A17" s="5" t="s">
-        <v>60</v>
-      </c>
-      <c r="B17" s="7" t="s">
-        <v>173</v>
-      </c>
-      <c r="C17" s="5" t="s">
-        <v>174</v>
-      </c>
-      <c r="D17" s="7" t="s">
-        <v>175</v>
-      </c>
-      <c r="E17" s="7" t="s">
-        <v>45</v>
-      </c>
-      <c r="F17" s="5" t="s">
-        <v>176</v>
-      </c>
-      <c r="G17" s="7" t="s">
-        <v>65</v>
-      </c>
-      <c r="H17" s="9" t="s">
-        <v>68</v>
-      </c>
-      <c r="I17" s="11" t="s">
-        <v>28</v>
-      </c>
-      <c r="J17" s="12" t="s">
-        <v>69</v>
-      </c>
-      <c r="K17" s="5" t="s">
-        <v>177</v>
-      </c>
-    </row>
     <row r="18">
       <c r="A18" s="5" t="s">
         <v>60</v>
@@ -10282,39 +10258,61 @@
         <v>177</v>
       </c>
     </row>
-    <row r="20">
-      <c r="A20" s="5" t="s">
-        <v>60</v>
-      </c>
-      <c r="B20" s="7" t="s">
-        <v>187</v>
-      </c>
-      <c r="C20" s="5" t="s">
-        <v>188</v>
-      </c>
-      <c r="D20" s="7" t="s">
-        <v>44</v>
-      </c>
-      <c r="E20" s="7" t="s">
-        <v>45</v>
-      </c>
-      <c r="F20" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="G20" s="7" t="s">
-        <v>65</v>
-      </c>
-      <c r="H20" s="9" t="s">
-        <v>68</v>
-      </c>
-      <c r="I20" s="11" t="s">
-        <v>28</v>
-      </c>
-      <c r="J20" s="12" t="s">
-        <v>69</v>
-      </c>
-      <c r="K20" s="5" t="s">
-        <v>177</v>
+    <row r="20" ht="15.75" customHeight="1">
+      <c r="A20" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">C-1.2</t>
+        </is>
+      </c>
+      <c r="B20" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">C-1.2-a</t>
+        </is>
+      </c>
+      <c r="C20" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">At least one declared or standard-location parent sitemap reaches a final HTTP 200 (directly, or through a redirect chain)</t>
+        </is>
+      </c>
+      <c r="D20" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PASS</t>
+        </is>
+      </c>
+      <c r="E20" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">—</t>
+        </is>
+      </c>
+      <c r="F20" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">—</t>
+        </is>
+      </c>
+      <c r="G20" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">G5, G6, G2, P1</t>
+        </is>
+      </c>
+      <c r="H20" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://developers.google.com/search/docs/crawling-indexing/sitemaps/build-sitemap</t>
+        </is>
+      </c>
+      <c r="I20" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Google — documented</t>
+        </is>
+      </c>
+      <c r="J20" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Tool policy</t>
+        </is>
+      </c>
+      <c r="K20" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Inherits the factor-level source. Google documents the Sitemap: directive as a location source and sitemaps.org defines the root elements. PASS asks only that a parent sitemap can be located and fetched; the number of hostnames that also serve it is not a sitemap condition.</t>
+        </is>
       </c>
     </row>
     <row r="21" ht="15.75" customHeight="1">
@@ -20514,17 +20512,6 @@
         <v>1401</v>
       </c>
     </row>
-    <row r="324" ht="15.75" customHeight="1"/>
-    <row r="325" ht="15.75" customHeight="1"/>
-    <row r="326" ht="15.75" customHeight="1"/>
-    <row r="327" ht="15.75" customHeight="1"/>
-    <row r="328" ht="15.75" customHeight="1"/>
-    <row r="329" ht="15.75" customHeight="1"/>
-    <row r="330" ht="15.75" customHeight="1"/>
-    <row r="331" ht="15.75" customHeight="1"/>
-    <row r="332" ht="15.75" customHeight="1"/>
-    <row r="333" ht="15.75" customHeight="1"/>
-    <row r="334" ht="15.75" customHeight="1"/>
     <row r="335" ht="15.75" customHeight="1"/>
     <row r="336" ht="15.75" customHeight="1"/>
     <row r="337" ht="15.75" customHeight="1"/>
@@ -21191,6 +21178,576 @@
     <row r="998" ht="15.75" customHeight="1"/>
     <row r="999" ht="15.75" customHeight="1"/>
     <row r="1000" ht="15.75" customHeight="1"/>
+    <row r="324" ht="15.75" customHeight="1">
+      <c r="A324" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">C-1.1</t>
+        </is>
+      </c>
+      <c r="B324" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">C-1.1-l</t>
+        </is>
+      </c>
+      <c r="C324" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Disallow: / applies to Googlebot on a host the operator declared as staging (env = staging)</t>
+        </is>
+      </c>
+      <c r="D324" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WARN</t>
+        </is>
+      </c>
+      <c r="E324" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LOW</t>
+        </is>
+      </c>
+      <c r="F324" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">STAGING_BLOCK_EXPECTED</t>
+        </is>
+      </c>
+      <c r="G324" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">G1, G1b</t>
+        </is>
+      </c>
+      <c r="H324" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://developers.google.com/search/docs/crawling-indexing/robots/robots_txt</t>
+        </is>
+      </c>
+      <c r="I324" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Google — documented</t>
+        </is>
+      </c>
+      <c r="J324" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Tool policy</t>
+        </is>
+      </c>
+      <c r="K324" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">E-1.1-12. The directive is read exactly as the Google specification documents it. That a sitewide block is expected here is operator-supplied context, not something any source can establish, so the downgrade from CRITICAL is tool policy.</t>
+        </is>
+      </c>
+    </row>
+    <row r="326" ht="15.75" customHeight="1">
+      <c r="A326" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">C-1.3</t>
+        </is>
+      </c>
+      <c r="B326" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">C-1.3-s</t>
+        </is>
+      </c>
+      <c r="C326" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">HTTP 503 accompanied by a Retry-After header</t>
+        </is>
+      </c>
+      <c r="D326" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WARN</t>
+        </is>
+      </c>
+      <c r="E326" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">MEDIUM</t>
+        </is>
+      </c>
+      <c r="F326" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">MAINTENANCE_MODE</t>
+        </is>
+      </c>
+      <c r="G326" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">G2</t>
+        </is>
+      </c>
+      <c r="H326" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://developers.google.com/search/docs/crawling-indexing/http-network-errors</t>
+        </is>
+      </c>
+      <c r="I326" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Google — documented</t>
+        </is>
+      </c>
+      <c r="J326" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Tool policy</t>
+        </is>
+      </c>
+      <c r="K326" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">E-1.3-3. Google documents 503 with Retry-After as the correct way to signal temporary unavailability, so it is not scored as a server error. Whether the maintenance is intentional is not observable.</t>
+        </is>
+      </c>
+    </row>
+    <row r="327" ht="15.75" customHeight="1">
+      <c r="A327" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">C-1.4</t>
+        </is>
+      </c>
+      <c r="B327" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">C-1.4-p</t>
+        </is>
+      </c>
+      <c r="C327" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Both the trailing-slash and the no-slash form return 2xx and neither redirects to the other</t>
+        </is>
+      </c>
+      <c r="D327" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">FAIL</t>
+        </is>
+      </c>
+      <c r="E327" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">HIGH</t>
+        </is>
+      </c>
+      <c r="F327" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TRAILING_SLASH_BOTH_LIVE</t>
+        </is>
+      </c>
+      <c r="G327" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">G7, G2</t>
+        </is>
+      </c>
+      <c r="H327" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://developers.google.com/search/docs/crawling-indexing/consolidate-duplicate-urls</t>
+        </is>
+      </c>
+      <c r="I327" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Google — documented</t>
+        </is>
+      </c>
+      <c r="J327" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Tool policy</t>
+        </is>
+      </c>
+      <c r="K327" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Operator rule, added after a live audit. Google documents that the same content reachable at several URLs must be consolidated to one canonical form; the document does not assign a severity, so FAIL/HIGH is tool policy.</t>
+        </is>
+      </c>
+    </row>
+    <row r="328" ht="15.75" customHeight="1">
+      <c r="A328" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">C-1.5</t>
+        </is>
+      </c>
+      <c r="B328" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">C-1.5-u</t>
+        </is>
+      </c>
+      <c r="C328" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">More than one link[rel=canonical] in &lt;head&gt;, all carrying the same value</t>
+        </is>
+      </c>
+      <c r="D328" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WARN</t>
+        </is>
+      </c>
+      <c r="E328" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LOW</t>
+        </is>
+      </c>
+      <c r="F328" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CANONICAL_DUPLICATED_IDENTICAL</t>
+        </is>
+      </c>
+      <c r="G328" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">G7</t>
+        </is>
+      </c>
+      <c r="H328" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://developers.google.com/search/docs/crawling-indexing/consolidate-duplicate-urls</t>
+        </is>
+      </c>
+      <c r="I328" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Google — documented</t>
+        </is>
+      </c>
+      <c r="J328" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Tool policy</t>
+        </is>
+      </c>
+      <c r="K328" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">E-1.5-6. Google documents that conflicting canonicals may all be ignored; duplicates that agree are unambiguous, so this is a tidiness warning and not the conflicting-canonical failure.</t>
+        </is>
+      </c>
+    </row>
+    <row r="329" ht="15.75" customHeight="1">
+      <c r="A329" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">C-1.6</t>
+        </is>
+      </c>
+      <c r="B329" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">C-1.6-o</t>
+        </is>
+      </c>
+      <c r="C329" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Effective noindex for Googlebot on a host the operator declared as staging (env = staging)</t>
+        </is>
+      </c>
+      <c r="D329" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WARN</t>
+        </is>
+      </c>
+      <c r="E329" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LOW</t>
+        </is>
+      </c>
+      <c r="F329" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">STAGING_NOINDEX_EXPECTED</t>
+        </is>
+      </c>
+      <c r="G329" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">G8</t>
+        </is>
+      </c>
+      <c r="H329" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://developers.google.com/search/docs/crawling-indexing/robots-meta-tag</t>
+        </is>
+      </c>
+      <c r="I329" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Google — documented</t>
+        </is>
+      </c>
+      <c r="J329" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Tool policy</t>
+        </is>
+      </c>
+      <c r="K329" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">E-1.6-8. The directive is read as documented. That noindex is expected on staging is operator-supplied context, so the downgrade from CRITICAL is tool policy.</t>
+        </is>
+      </c>
+    </row>
+    <row r="330" ht="15.75" customHeight="1">
+      <c r="A330" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">C-1.6</t>
+        </is>
+      </c>
+      <c r="B330" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">C-1.6-p</t>
+        </is>
+      </c>
+      <c r="C330" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">A meta robots element appears inside &lt;noscript&gt;</t>
+        </is>
+      </c>
+      <c r="D330" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WARN</t>
+        </is>
+      </c>
+      <c r="E330" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">HIGH</t>
+        </is>
+      </c>
+      <c r="F330" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">META_ROBOTS_IN_NOSCRIPT</t>
+        </is>
+      </c>
+      <c r="G330" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">G8</t>
+        </is>
+      </c>
+      <c r="H330" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://developers.google.com/search/docs/crawling-indexing/robots-meta-tag</t>
+        </is>
+      </c>
+      <c r="I330" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Google — documented</t>
+        </is>
+      </c>
+      <c r="J330" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Tool policy</t>
+        </is>
+      </c>
+      <c r="K330" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">E-1.6-10. Google documents where robots meta tags are honoured; it does not document behaviour inside &lt;noscript&gt;, which is why the finding reports inconsistency rather than asserting a specific outcome.</t>
+        </is>
+      </c>
+    </row>
+    <row r="331" ht="15.75" customHeight="1">
+      <c r="A331" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">C-3.2</t>
+        </is>
+      </c>
+      <c r="B331" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">C-3.2-t</t>
+        </is>
+      </c>
+      <c r="C331" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Exactly one weak multilingual signal observed and no hreflang annotations present</t>
+        </is>
+      </c>
+      <c r="D331" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WARN</t>
+        </is>
+      </c>
+      <c r="E331" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">MEDIUM</t>
+        </is>
+      </c>
+      <c r="F331" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">HREFLANG_POSSIBLY_MISSING</t>
+        </is>
+      </c>
+      <c r="G331" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">G10</t>
+        </is>
+      </c>
+      <c r="H331" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://developers.google.com/search/docs/specialty/international/localized-versions</t>
+        </is>
+      </c>
+      <c r="I331" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Google — documented</t>
+        </is>
+      </c>
+      <c r="J331" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Tool policy</t>
+        </is>
+      </c>
+      <c r="K331" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">B-3.2-3. Advisory only: a single weak signal is not evidence that the site is multilingual, so this never reaches the hreflang-absent failure.</t>
+        </is>
+      </c>
+    </row>
+    <row r="332" ht="15.75" customHeight="1">
+      <c r="A332" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">C-5.3</t>
+        </is>
+      </c>
+      <c r="B332" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">C-5.3-o</t>
+        </is>
+      </c>
+      <c r="C332" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">llms.txt is a flat list of URLs with no H2 sections and no descriptions</t>
+        </is>
+      </c>
+      <c r="D332" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WARN</t>
+        </is>
+      </c>
+      <c r="E332" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LOW</t>
+        </is>
+      </c>
+      <c r="F332" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LLMS_TXT_SITEMAP_CLONE</t>
+        </is>
+      </c>
+      <c r="G332" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">L1, G16</t>
+        </is>
+      </c>
+      <c r="H332" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://llmstxt.org/</t>
+        </is>
+      </c>
+      <c r="I332" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Proposed — not adopted</t>
+        </is>
+      </c>
+      <c r="J332" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Tool policy</t>
+        </is>
+      </c>
+      <c r="K332" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">The file conforms to the proposed specification, which requires only an H1. That a flat URL list is low value is a judgement this tool makes, not a requirement of the specification — and llms.txt is not adopted by any search engine.</t>
+        </is>
+      </c>
+    </row>
+    <row r="333" ht="15.75" customHeight="1">
+      <c r="A333" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">C-1.2</t>
+        </is>
+      </c>
+      <c r="B333" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">C-1.2-j</t>
+        </is>
+      </c>
+      <c r="C333" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">A declared sitemap is unavailable on every variant, while another declared or standard-location parent sitemap returns 200</t>
+        </is>
+      </c>
+      <c r="D333" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WARN</t>
+        </is>
+      </c>
+      <c r="E333" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">MEDIUM</t>
+        </is>
+      </c>
+      <c r="F333" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">SITEMAP_PARTIALLY_BROKEN</t>
+        </is>
+      </c>
+      <c r="G333" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">G5, G2</t>
+        </is>
+      </c>
+      <c r="H333" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://developers.google.com/search/docs/crawling-indexing/sitemaps/build-sitemap</t>
+        </is>
+      </c>
+      <c r="I333" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Google — documented</t>
+        </is>
+      </c>
+      <c r="J333" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Tool policy</t>
+        </is>
+      </c>
+      <c r="K333" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">The sitemap setup works, but robots.txt advertises a URL that is not there. Usable, so not a failure; misleading, so not silent.</t>
+        </is>
+      </c>
+    </row>
+    <row r="334" ht="15.75" customHeight="1">
+      <c r="A334" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">C-1.2</t>
+        </is>
+      </c>
+      <c r="B334" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">C-1.2-k</t>
+        </is>
+      </c>
+      <c r="C334" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">A sitemap endpoint responds but never reaches a successful response: a 5xx, or a redirect chain that resolves to a 4xx</t>
+        </is>
+      </c>
+      <c r="D334" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">FAIL</t>
+        </is>
+      </c>
+      <c r="E334" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">HIGH</t>
+        </is>
+      </c>
+      <c r="F334" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">SITEMAP_UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="G334" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">G5, G2</t>
+        </is>
+      </c>
+      <c r="H334" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://developers.google.com/search/docs/crawling-indexing/sitemaps/build-sitemap</t>
+        </is>
+      </c>
+      <c r="I334" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Google — documented</t>
+        </is>
+      </c>
+      <c r="J334" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Tool policy</t>
+        </is>
+      </c>
+      <c r="K334" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Distinct from "not found". A clean 404 at a standard location means no sitemap is published there, which is only a warning. An endpoint that answers and then fails is a sitemap that exists and does not serve.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="$A$1:$K$323"/>
   <hyperlinks>

--- a/technicalaudittoolPRD_v2_source_register.xlsx
+++ b/technicalaudittoolPRD_v2_source_register.xlsx
@@ -6949,9 +6949,6 @@
         <v>950</v>
       </c>
     </row>
-    <row r="47" ht="15.75" customHeight="1"/>
-    <row r="48" ht="15.75" customHeight="1"/>
-    <row r="49" ht="15.75" customHeight="1"/>
     <row r="50" ht="15.75" customHeight="1"/>
     <row r="51" ht="15.75" customHeight="1"/>
     <row r="52" ht="15.75" customHeight="1"/>
@@ -7903,6 +7900,117 @@
     <row r="998" ht="15.75" customHeight="1"/>
     <row r="999" ht="15.75" customHeight="1"/>
     <row r="1000" ht="15.75" customHeight="1"/>
+    <row r="47" ht="15.75" customHeight="1">
+      <c r="A47" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">GSO</t>
+        </is>
+      </c>
+      <c r="B47" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Google</t>
+        </is>
+      </c>
+      <c r="C47" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Refine web searches (search operators, including site:)</t>
+        </is>
+      </c>
+      <c r="D47" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://support.google.com/websearch/answer/2466433</t>
+        </is>
+      </c>
+      <c r="E47" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Google — documented</t>
+        </is>
+      </c>
+      <c r="F47" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Yes</t>
+        </is>
+      </c>
+      <c r="G47" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Documents the site: operator and states that result counts are estimates. Supports reading a site: query as evidence that a domain is or is not present in the index, and nothing finer.</t>
+        </is>
+      </c>
+    </row>
+    <row r="48" ht="15.75" customHeight="1">
+      <c r="A48" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">GSC</t>
+        </is>
+      </c>
+      <c r="B48" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Google Search Central</t>
+        </is>
+      </c>
+      <c r="C48" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Get started with Search Console</t>
+        </is>
+      </c>
+      <c r="D48" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://developers.google.com/search/docs/monitor-debug/search-console-start</t>
+        </is>
+      </c>
+      <c r="E48" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Google — documented</t>
+        </is>
+      </c>
+      <c r="F48" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Yes</t>
+        </is>
+      </c>
+      <c r="G48" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">The authoritative report on index coverage, available only to a verified owner. Cited wherever a SERP sample is used in its place, so the weaker evidence is never presented as the stronger.</t>
+        </is>
+      </c>
+    </row>
+    <row r="49" ht="15.75" customHeight="1">
+      <c r="A49" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CLR</t>
+        </is>
+      </c>
+      <c r="B49" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Cloro</t>
+        </is>
+      </c>
+      <c r="C49" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">SERP API</t>
+        </is>
+      </c>
+      <c r="D49" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://cloro.dev/serp-api/</t>
+        </is>
+      </c>
+      <c r="E49" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Third-party API — data provider</t>
+        </is>
+      </c>
+      <c r="F49" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Yes</t>
+        </is>
+      </c>
+      <c r="G49" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">The provider through which the site: query is executed. A data source, not an authority: it reports what Google returned and documents nothing about how search works.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="$A$1:$G$46"/>
   <hyperlinks>
@@ -8599,7 +8707,6 @@
         <v>590</v>
       </c>
     </row>
-    <row r="25" ht="15.75" customHeight="1"/>
     <row r="26" ht="15.75" customHeight="1"/>
     <row r="27" ht="15.75" customHeight="1"/>
     <row r="28" ht="15.75" customHeight="1"/>
@@ -9575,6 +9682,48 @@
     <row r="998" ht="15.75" customHeight="1"/>
     <row r="999" ht="15.75" customHeight="1"/>
     <row r="1000" ht="15.75" customHeight="1"/>
+    <row r="25" ht="15.75" customHeight="1">
+      <c r="A25" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">X-1.8</t>
+        </is>
+      </c>
+      <c r="B25" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Googlebot Access (using SERP)</t>
+        </is>
+      </c>
+      <c r="C25" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">SECTION 1 — CRAWL &amp; INDEXING</t>
+        </is>
+      </c>
+      <c r="D25" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3.0</t>
+        </is>
+      </c>
+      <c r="E25" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">GSO, GSC, CLR</t>
+        </is>
+      </c>
+      <c r="F25" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://support.google.com/websearch/answer/2466433</t>
+        </is>
+      </c>
+      <c r="G25" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Google — documented</t>
+        </is>
+      </c>
+      <c r="H25" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Google documents the site: operator and states that its counts are estimates. That supports one inference only: whether the domain is present in the index. Coverage is not measurable this way, and Search Console remains the authoritative report.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="$A$1:$H$24"/>
   <hyperlinks>
@@ -20512,10 +20661,7 @@
         <v>1401</v>
       </c>
     </row>
-    <row r="335" ht="15.75" customHeight="1"/>
-    <row r="336" ht="15.75" customHeight="1"/>
     <row r="337" ht="15.75" customHeight="1"/>
-    <row r="338" ht="15.75" customHeight="1"/>
     <row r="339" ht="15.75" customHeight="1"/>
     <row r="340" ht="15.75" customHeight="1"/>
     <row r="341" ht="15.75" customHeight="1"/>
@@ -21694,42 +21840,42 @@
     <row r="334" ht="15.75" customHeight="1">
       <c r="A334" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">C-1.2</t>
+          <t xml:space="preserve">X-1.8</t>
         </is>
       </c>
       <c r="B334" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">C-1.2-k</t>
+          <t xml:space="preserve">X-1.8-a</t>
         </is>
       </c>
       <c r="C334" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">A sitemap endpoint responds but never reaches a successful response: a 5xx, or a redirect chain that resolves to a 4xx</t>
+          <t xml:space="preserve">A site: query for the canonical host returns at least one organic result belonging to that host</t>
         </is>
       </c>
       <c r="D334" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">FAIL</t>
+          <t xml:space="preserve">PASS</t>
         </is>
       </c>
       <c r="E334" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">HIGH</t>
+          <t xml:space="preserve">—</t>
         </is>
       </c>
       <c r="F334" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">SITEMAP_UNAVAILABLE</t>
+          <t xml:space="preserve">—</t>
         </is>
       </c>
       <c r="G334" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">G5, G2</t>
+          <t xml:space="preserve">GSO, CLR</t>
         </is>
       </c>
       <c r="H334" s="9" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://developers.google.com/search/docs/crawling-indexing/sitemaps/build-sitemap</t>
+          <t xml:space="preserve">https://support.google.com/websearch/answer/2466433</t>
         </is>
       </c>
       <c r="I334" s="11" t="inlineStr">
@@ -21743,6 +21889,177 @@
         </is>
       </c>
       <c r="K334" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Google documents the site: operator. That a non-empty result set means the domain is present in the index follows directly; how much of it is present does not, and is not claimed.</t>
+        </is>
+      </c>
+    </row>
+    <row r="335" ht="15.75" customHeight="1">
+      <c r="A335" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">X-1.8</t>
+        </is>
+      </c>
+      <c r="B335" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">X-1.8-b</t>
+        </is>
+      </c>
+      <c r="C335" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">A site: query for the canonical host returns no organic results belonging to that host</t>
+        </is>
+      </c>
+      <c r="D335" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">FAIL</t>
+        </is>
+      </c>
+      <c r="E335" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CRITICAL</t>
+        </is>
+      </c>
+      <c r="F335" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">SITE_NOT_IN_INDEX</t>
+        </is>
+      </c>
+      <c r="G335" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">GSO, GSC</t>
+        </is>
+      </c>
+      <c r="H335" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://support.google.com/websearch/answer/2466433</t>
+        </is>
+      </c>
+      <c r="I335" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Google — documented</t>
+        </is>
+      </c>
+      <c r="J335" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Tool policy</t>
+        </is>
+      </c>
+      <c r="K335" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">An empty site: result set is the one strong inference the operator supports: Google is returning nothing for the domain. Severity is tool policy — a site absent from the index cannot rank at all, whatever else is configured correctly. Search Console (GSC) is the authoritative confirmation and needs the owner.</t>
+        </is>
+      </c>
+    </row>
+    <row r="336" ht="15.75" customHeight="1">
+      <c r="A336" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">X-1.8</t>
+        </is>
+      </c>
+      <c r="B336" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">X-1.8-c</t>
+        </is>
+      </c>
+      <c r="C336" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">The SERP lookup could not be completed: no key, key rejected, quota exhausted, timeout, or cap.serp_api = false</t>
+        </is>
+      </c>
+      <c r="D336" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NOT_TESTABLE</t>
+        </is>
+      </c>
+      <c r="E336" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">—</t>
+        </is>
+      </c>
+      <c r="F336" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">SERP_LOOKUP_UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="G336" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">GSO, CLR</t>
+        </is>
+      </c>
+      <c r="H336" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://support.google.com/websearch/answer/2466433</t>
+        </is>
+      </c>
+      <c r="I336" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Google — documented</t>
+        </is>
+      </c>
+      <c r="J336" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Tool policy</t>
+        </is>
+      </c>
+      <c r="K336" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Inherits the factor-level source. A lookup the tool could not complete says nothing about the site, so the result is excluded from the score rather than reported as absence.</t>
+        </is>
+      </c>
+    </row>
+    <row r="338" ht="15.75" customHeight="1">
+      <c r="A338" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">C-1.2</t>
+        </is>
+      </c>
+      <c r="B338" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">C-1.2-k</t>
+        </is>
+      </c>
+      <c r="C338" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">A sitemap endpoint responds but never reaches a successful response: a 5xx, or a redirect chain that resolves to a 4xx</t>
+        </is>
+      </c>
+      <c r="D338" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">FAIL</t>
+        </is>
+      </c>
+      <c r="E338" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">HIGH</t>
+        </is>
+      </c>
+      <c r="F338" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">SITEMAP_UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="G338" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">G5, G2</t>
+        </is>
+      </c>
+      <c r="H338" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://developers.google.com/search/docs/crawling-indexing/sitemaps/build-sitemap</t>
+        </is>
+      </c>
+      <c r="I338" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Google — documented</t>
+        </is>
+      </c>
+      <c r="J338" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Tool policy</t>
+        </is>
+      </c>
+      <c r="K338" s="5" t="inlineStr">
         <is>
           <t xml:space="preserve">Distinct from "not found". A clean 404 at a standard location means no sitemap is published there, which is only a warning. An endpoint that answers and then fails is a sitemap that exists and does not serve.</t>
         </is>

--- a/technicalaudittoolPRD_v2_source_register.xlsx
+++ b/technicalaudittoolPRD_v2_source_register.xlsx
@@ -14852,36 +14852,60 @@
       </c>
     </row>
     <row r="152" ht="15.75" customHeight="1">
-      <c r="A152" s="5" t="s">
-        <v>297</v>
-      </c>
-      <c r="B152" s="7" t="s">
-        <v>1067</v>
-      </c>
-      <c r="C152" s="5" t="s">
-        <v>1068</v>
-      </c>
-      <c r="D152" s="7" t="s">
-        <v>55</v>
-      </c>
-      <c r="E152" s="7" t="s">
-        <v>66</v>
-      </c>
-      <c r="F152" s="5" t="s">
-        <v>1069</v>
-      </c>
-      <c r="G152" s="7" t="s">
-        <v>235</v>
-      </c>
-      <c r="H152" s="9" t="s">
-        <v>238</v>
-      </c>
-      <c r="I152" s="11" t="s">
-        <v>28</v>
-      </c>
-      <c r="J152" s="7"/>
-      <c r="K152" s="5" t="s">
-        <v>1070</v>
+      <c r="A152" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">C-3.1</t>
+        </is>
+      </c>
+      <c r="B152" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">C-3.1-b</t>
+        </is>
+      </c>
+      <c r="C152" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">No structured data of any kind on the page</t>
+        </is>
+      </c>
+      <c r="D152" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WARN</t>
+        </is>
+      </c>
+      <c r="E152" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">MEDIUM</t>
+        </is>
+      </c>
+      <c r="F152" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NO_STRUCTURED_DATA</t>
+        </is>
+      </c>
+      <c r="G152" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">G11</t>
+        </is>
+      </c>
+      <c r="H152" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://developers.google.com/search/docs/appearance/structured-data/sd-policies</t>
+        </is>
+      </c>
+      <c r="I152" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Google — documented</t>
+        </is>
+      </c>
+      <c r="J152" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Tool policy</t>
+        </is>
+      </c>
+      <c r="K152" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Downgraded from FAIL/HIGH. Google documents structured data as what makes a page eligible for rich results; it does not document markup as a requirement for crawling, indexing or ranking. A page without it is missing an opportunity, not broken, and calling that a failure overstates what the absence means. The grading is tool policy, as the previous row also recorded.</t>
+        </is>
       </c>
     </row>
     <row r="153" ht="15.75" customHeight="1">
@@ -18711,38 +18735,60 @@
       </c>
     </row>
     <row r="267" ht="15.75" customHeight="1">
-      <c r="A267" s="5" t="s">
-        <v>481</v>
-      </c>
-      <c r="B267" s="7" t="s">
-        <v>661</v>
-      </c>
-      <c r="C267" s="5" t="s">
-        <v>663</v>
-      </c>
-      <c r="D267" s="7" t="s">
-        <v>55</v>
-      </c>
-      <c r="E267" s="7" t="s">
-        <v>56</v>
-      </c>
-      <c r="F267" s="5" t="s">
-        <v>664</v>
-      </c>
-      <c r="G267" s="7" t="s">
-        <v>195</v>
-      </c>
-      <c r="H267" s="9" t="s">
-        <v>198</v>
-      </c>
-      <c r="I267" s="11" t="s">
-        <v>28</v>
-      </c>
-      <c r="J267" s="12" t="s">
-        <v>69</v>
-      </c>
-      <c r="K267" s="5" t="s">
-        <v>1351</v>
+      <c r="A267" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">C-6.1</t>
+        </is>
+      </c>
+      <c r="B267" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">C-6.1-b</t>
+        </is>
+      </c>
+      <c r="C267" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Main content &lt; 50 words in RAW on a page that passed the A0 validity gate, AND the rendered DOM carries at least 3x the raw word count (minimum 50)</t>
+        </is>
+      </c>
+      <c r="D267" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">FAIL</t>
+        </is>
+      </c>
+      <c r="E267" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CRITICAL</t>
+        </is>
+      </c>
+      <c r="F267" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">RAW_CONTENT_ABSENT</t>
+        </is>
+      </c>
+      <c r="G267" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">G9, TP</t>
+        </is>
+      </c>
+      <c r="H267" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://developers.google.com/search/docs/crawling-indexing/javascript/javascript-seo-basics</t>
+        </is>
+      </c>
+      <c r="I267" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Google — documented</t>
+        </is>
+      </c>
+      <c r="J267" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Tool policy</t>
+        </is>
+      </c>
+      <c r="K267" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Both halves are required. The rule previously fired on the raw word count alone and asserted JavaScript gating whenever a rendered profile existed, without comparing the two — so a page with 8 words raw and 8 rendered was reported as JavaScript-gated. Google documents the raw/rendered distinction; the thresholds are tool policy.</t>
+        </is>
       </c>
     </row>
     <row r="268" ht="15.75" customHeight="1">
@@ -20662,7 +20708,6 @@
       </c>
     </row>
     <row r="337" ht="15.75" customHeight="1"/>
-    <row r="339" ht="15.75" customHeight="1"/>
     <row r="340" ht="15.75" customHeight="1"/>
     <row r="341" ht="15.75" customHeight="1"/>
     <row r="342" ht="15.75" customHeight="1"/>
@@ -21907,7 +21952,7 @@
       </c>
       <c r="C335" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">A site: query for the canonical host returns no organic results belonging to that host</t>
+          <t xml:space="preserve">A site: query for the canonical host returns no organic result belonging to that host</t>
         </is>
       </c>
       <c r="D335" s="7" t="inlineStr">
@@ -21917,7 +21962,7 @@
       </c>
       <c r="E335" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">CRITICAL</t>
+          <t xml:space="preserve">HIGH</t>
         </is>
       </c>
       <c r="F335" s="5" t="inlineStr">
@@ -21947,7 +21992,7 @@
       </c>
       <c r="K335" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">An empty site: result set is the one strong inference the operator supports: Google is returning nothing for the domain. Severity is tool policy — a site absent from the index cannot rank at all, whatever else is configured correctly. Search Console (GSC) is the authoritative confirmation and needs the owner.</t>
+          <t xml:space="preserve">Downgraded from CRITICAL so it cannot cap the overall score. A CRITICAL caps the audit at 40, and this finding rests on a third-party SERP sample of a query whose counts Google itself calls estimates — evidence strong enough to report prominently, not strong enough to let a provider outage decide a client’s headline number. Search Console (GSC) remains the authoritative confirmation.</t>
         </is>
       </c>
     </row>
@@ -22062,6 +22107,63 @@
       <c r="K338" s="5" t="inlineStr">
         <is>
           <t xml:space="preserve">Distinct from "not found". A clean 404 at a standard location means no sitemap is published there, which is only a warning. An endpoint that answers and then fails is a sitemap that exists and does not serve.</t>
+        </is>
+      </c>
+    </row>
+    <row r="339" ht="15.75" customHeight="1">
+      <c r="A339" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">C-6.1</t>
+        </is>
+      </c>
+      <c r="B339" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">C-6.1-p</t>
+        </is>
+      </c>
+      <c r="C339" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Main content &lt; 50 words in RAW on a page that passed the A0 validity gate, and rendering does not materially increase it</t>
+        </is>
+      </c>
+      <c r="D339" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WARN</t>
+        </is>
+      </c>
+      <c r="E339" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">MEDIUM</t>
+        </is>
+      </c>
+      <c r="F339" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">RAW_CONTENT_THIN_VALID_PAGE</t>
+        </is>
+      </c>
+      <c r="G339" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">G9, TP</t>
+        </is>
+      </c>
+      <c r="H339" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://developers.google.com/search/docs/crawling-indexing/javascript/javascript-seo-basics</t>
+        </is>
+      </c>
+      <c r="I339" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Google — documented</t>
+        </is>
+      </c>
+      <c r="J339" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Tool policy</t>
+        </is>
+      </c>
+      <c r="K339" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Distinct from C-6.1-b. Google documents that content assembled by scripts may not be seen by every consumer, which is what C-6.1-b reports. Where rendering adds nothing, JavaScript is not withholding anything and the page is simply thin — worth reporting, but not the same defect and not critical. The 50-word boundary and the 3x rendering ratio are tool policy.</t>
         </is>
       </c>
     </row>

--- a/technicalaudittoolPRD_v2_source_register.xlsx
+++ b/technicalaudittoolPRD_v2_source_register.xlsx
@@ -6950,7 +6950,6 @@
       </c>
     </row>
     <row r="50" ht="15.75" customHeight="1"/>
-    <row r="51" ht="15.75" customHeight="1"/>
     <row r="52" ht="15.75" customHeight="1"/>
     <row r="53" ht="15.75" customHeight="1"/>
     <row r="54" ht="15.75" customHeight="1"/>
@@ -8011,6 +8010,43 @@
         </is>
       </c>
     </row>
+    <row r="51" ht="15.75" customHeight="1">
+      <c r="A51" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CC</t>
+        </is>
+      </c>
+      <c r="B51" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Common Crawl</t>
+        </is>
+      </c>
+      <c r="C51" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Common Crawl open web archive</t>
+        </is>
+      </c>
+      <c r="D51" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://commoncrawl.org/</t>
+        </is>
+      </c>
+      <c r="E51" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Third-party archive — not a search index</t>
+        </is>
+      </c>
+      <c r="F51" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Yes</t>
+        </is>
+      </c>
+      <c r="G51" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">An open repository of web crawl data. Supports one inference: a URL was captured in a given crawl. It documents nothing about search ranking, indexing, model training, or whether any assistant will cite a page.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="$A$1:$G$46"/>
   <hyperlinks>
@@ -8708,8 +8744,6 @@
       </c>
     </row>
     <row r="26" ht="15.75" customHeight="1"/>
-    <row r="27" ht="15.75" customHeight="1"/>
-    <row r="28" ht="15.75" customHeight="1"/>
     <row r="29" ht="15.75" customHeight="1"/>
     <row r="30" ht="15.75" customHeight="1"/>
     <row r="31" ht="15.75" customHeight="1"/>
@@ -9724,6 +9758,90 @@
         </is>
       </c>
     </row>
+    <row r="27" ht="15.75" customHeight="1">
+      <c r="A27" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">X-5.3b</t>
+        </is>
+      </c>
+      <c r="B27" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LLms-full.txt</t>
+        </is>
+      </c>
+      <c r="C27" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">SECTION 5 — LLM / AI ACCESS</t>
+        </is>
+      </c>
+      <c r="D27" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4.0</t>
+        </is>
+      </c>
+      <c r="E27" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">L1, TP</t>
+        </is>
+      </c>
+      <c r="F27" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://llmstxt.org/</t>
+        </is>
+      </c>
+      <c r="G27" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Proposed — not adopted</t>
+        </is>
+      </c>
+      <c r="H27" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">llms-full.txt is not part of the llms.txt proposal and no search engine consumes it. Reported as information only; there is no requirement for it to meet.</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="15.75" customHeight="1">
+      <c r="A28" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">X-5.5</t>
+        </is>
+      </c>
+      <c r="B28" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Common Crawl presence</t>
+        </is>
+      </c>
+      <c r="C28" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">SECTION 5 — LLM / AI ACCESS</t>
+        </is>
+      </c>
+      <c r="D28" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4.0</t>
+        </is>
+      </c>
+      <c r="E28" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CC, TP</t>
+        </is>
+      </c>
+      <c r="F28" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://commoncrawl.org/</t>
+        </is>
+      </c>
+      <c r="G28" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Third-party archive — not a search index</t>
+        </is>
+      </c>
+      <c r="H28" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Presence in an open web archive. Reported as information only. Treating it as an AI-visibility or SEO outcome would claim more than the archive supports.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="$A$1:$H$24"/>
   <hyperlinks>
@@ -11151,38 +11269,60 @@
       </c>
     </row>
     <row r="41" ht="15.75" customHeight="1">
-      <c r="A41" s="5" t="s">
-        <v>127</v>
-      </c>
-      <c r="B41" s="7" t="s">
-        <v>321</v>
-      </c>
-      <c r="C41" s="5" t="s">
-        <v>322</v>
-      </c>
-      <c r="D41" s="7" t="s">
-        <v>55</v>
-      </c>
-      <c r="E41" s="7" t="s">
-        <v>66</v>
-      </c>
-      <c r="F41" s="5" t="s">
-        <v>323</v>
-      </c>
-      <c r="G41" s="7" t="s">
-        <v>132</v>
-      </c>
-      <c r="H41" s="9" t="s">
-        <v>74</v>
-      </c>
-      <c r="I41" s="11" t="s">
-        <v>28</v>
-      </c>
-      <c r="J41" s="12" t="s">
-        <v>69</v>
-      </c>
-      <c r="K41" s="5" t="s">
-        <v>317</v>
+      <c r="A41" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">C-1.4</t>
+        </is>
+      </c>
+      <c r="B41" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">C-1.4-c</t>
+        </is>
+      </c>
+      <c r="C41" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Two or more origin variants serve equivalent real content and none redirects to a single preferred origin</t>
+        </is>
+      </c>
+      <c r="D41" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WARN</t>
+        </is>
+      </c>
+      <c r="E41" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">HIGH</t>
+        </is>
+      </c>
+      <c r="F41" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">MULTIPLE_LIVE_ORIGINS</t>
+        </is>
+      </c>
+      <c r="G41" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">G7, G2</t>
+        </is>
+      </c>
+      <c r="H41" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://developers.google.com/search/docs/crawling-indexing/consolidate-duplicate-urls</t>
+        </is>
+      </c>
+      <c r="I41" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Google — documented</t>
+        </is>
+      </c>
+      <c r="J41" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Tool policy</t>
+        </is>
+      </c>
+      <c r="K41" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Downgraded from FAIL. Google documents that it consolidates duplicate URLs and picks a canonical itself, so a site reachable at several origins is diluting signals rather than failing. Reported prominently; not graded as breakage. The severity is tool policy.</t>
+        </is>
       </c>
     </row>
     <row r="42" ht="15.75" customHeight="1">
@@ -14009,36 +14149,60 @@
       </c>
     </row>
     <row r="127" ht="15.75" customHeight="1">
-      <c r="A127" s="5" t="s">
-        <v>262</v>
-      </c>
-      <c r="B127" s="7" t="s">
-        <v>1011</v>
-      </c>
-      <c r="C127" s="5" t="s">
-        <v>1012</v>
-      </c>
-      <c r="D127" s="7" t="s">
-        <v>55</v>
-      </c>
-      <c r="E127" s="7" t="s">
-        <v>104</v>
-      </c>
-      <c r="F127" s="5" t="s">
-        <v>1013</v>
-      </c>
-      <c r="G127" s="7" t="s">
-        <v>266</v>
-      </c>
-      <c r="H127" s="9" t="s">
-        <v>249</v>
-      </c>
-      <c r="I127" s="11" t="s">
-        <v>28</v>
-      </c>
-      <c r="J127" s="7"/>
-      <c r="K127" s="5" t="s">
-        <v>1010</v>
+      <c r="A127" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">C-2.3</t>
+        </is>
+      </c>
+      <c r="B127" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">C-2.3-b</t>
+        </is>
+      </c>
+      <c r="C127" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">No h1 in RAW or RENDERED on a page that passed the A0 validity gate</t>
+        </is>
+      </c>
+      <c r="D127" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WARN</t>
+        </is>
+      </c>
+      <c r="E127" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">MEDIUM</t>
+        </is>
+      </c>
+      <c r="F127" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">H1_MISSING</t>
+        </is>
+      </c>
+      <c r="G127" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">G18, A4</t>
+        </is>
+      </c>
+      <c r="H127" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://developers.google.com/search/docs/essentials/technical</t>
+        </is>
+      </c>
+      <c r="I127" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Google — documented</t>
+        </is>
+      </c>
+      <c r="J127" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Tool policy</t>
+        </is>
+      </c>
+      <c r="K127" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Downgraded from FAIL. Google documents headings as helping it understand page structure; it does not require an h1, and a page without one is still crawled, indexed and ranked. A missing h1 is a clarity problem worth fixing, not a defect. The grading is tool policy.</t>
+        </is>
       </c>
     </row>
     <row r="128" ht="15.75" customHeight="1">
@@ -14413,36 +14577,60 @@
       </c>
     </row>
     <row r="139" ht="15.75" customHeight="1">
-      <c r="A139" s="5" t="s">
-        <v>262</v>
-      </c>
-      <c r="B139" s="7" t="s">
-        <v>1035</v>
-      </c>
-      <c r="C139" s="5" t="s">
-        <v>1036</v>
-      </c>
-      <c r="D139" s="7" t="s">
-        <v>55</v>
-      </c>
-      <c r="E139" s="7" t="s">
-        <v>66</v>
-      </c>
-      <c r="F139" s="5" t="s">
-        <v>1037</v>
-      </c>
-      <c r="G139" s="7" t="s">
-        <v>266</v>
-      </c>
-      <c r="H139" s="9" t="s">
-        <v>249</v>
-      </c>
-      <c r="I139" s="11" t="s">
-        <v>28</v>
-      </c>
-      <c r="J139" s="7"/>
-      <c r="K139" s="5" t="s">
-        <v>1010</v>
+      <c r="A139" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">C-2.3</t>
+        </is>
+      </c>
+      <c r="B139" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">C-2.3-n</t>
+        </is>
+      </c>
+      <c r="C139" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Zero headings of any level on a page that passed the A0 validity gate</t>
+        </is>
+      </c>
+      <c r="D139" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WARN</t>
+        </is>
+      </c>
+      <c r="E139" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">MEDIUM</t>
+        </is>
+      </c>
+      <c r="F139" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NO_HEADINGS</t>
+        </is>
+      </c>
+      <c r="G139" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">G18, A4</t>
+        </is>
+      </c>
+      <c r="H139" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://developers.google.com/search/docs/essentials/technical</t>
+        </is>
+      </c>
+      <c r="I139" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Google — documented</t>
+        </is>
+      </c>
+      <c r="J139" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Tool policy</t>
+        </is>
+      </c>
+      <c r="K139" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Downgraded from FAIL/HIGH. The A0 gate now guarantees this is a real page rather than an interstitial, which is what previously produced this finding falsely. A page genuinely without headings is harder for a reader and an assistant to navigate, but it is not broken. The grading is tool policy.</t>
+        </is>
       </c>
     </row>
     <row r="140" ht="15.75" customHeight="1">
@@ -20708,14 +20896,6 @@
       </c>
     </row>
     <row r="337" ht="15.75" customHeight="1"/>
-    <row r="340" ht="15.75" customHeight="1"/>
-    <row r="341" ht="15.75" customHeight="1"/>
-    <row r="342" ht="15.75" customHeight="1"/>
-    <row r="343" ht="15.75" customHeight="1"/>
-    <row r="344" ht="15.75" customHeight="1"/>
-    <row r="345" ht="15.75" customHeight="1"/>
-    <row r="346" ht="15.75" customHeight="1"/>
-    <row r="347" ht="15.75" customHeight="1"/>
     <row r="348" ht="15.75" customHeight="1"/>
     <row r="349" ht="15.75" customHeight="1"/>
     <row r="350" ht="15.75" customHeight="1"/>
@@ -21957,7 +22137,7 @@
       </c>
       <c r="D335" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">FAIL</t>
+          <t xml:space="preserve">WARN</t>
         </is>
       </c>
       <c r="E335" s="7" t="inlineStr">
@@ -21992,7 +22172,7 @@
       </c>
       <c r="K335" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Downgraded from CRITICAL so it cannot cap the overall score. A CRITICAL caps the audit at 40, and this finding rests on a third-party SERP sample of a query whose counts Google itself calls estimates — evidence strong enough to report prominently, not strong enough to let a provider outage decide a client’s headline number. Search Console (GSC) remains the authoritative confirmation.</t>
+          <t xml:space="preserve">The factor is marked advisory in the catalogue, so this never enters a score. A site: query samples what Google will show for one operator whose counts Google itself calls estimates; it is not an index report and not a test of crawler access. Worth surfacing — an empty result is a strong prompt to check Search Console — but not something that should move a score it cannot support.</t>
         </is>
       </c>
     </row>
@@ -22164,6 +22344,462 @@
       <c r="K339" s="5" t="inlineStr">
         <is>
           <t xml:space="preserve">Distinct from C-6.1-b. Google documents that content assembled by scripts may not be seen by every consumer, which is what C-6.1-b reports. Where rendering adds nothing, JavaScript is not withholding anything and the page is simply thin — worth reporting, but not the same defect and not critical. The 50-word boundary and the 3x rendering ratio are tool policy.</t>
+        </is>
+      </c>
+    </row>
+    <row r="340" ht="15.75" customHeight="1">
+      <c r="A340" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">X-5.3b</t>
+        </is>
+      </c>
+      <c r="B340" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">X-5.3b-a</t>
+        </is>
+      </c>
+      <c r="C340" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">/llms-full.txt returns 200 with substantive non-HTML text</t>
+        </is>
+      </c>
+      <c r="D340" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PASS</t>
+        </is>
+      </c>
+      <c r="E340" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">—</t>
+        </is>
+      </c>
+      <c r="F340" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LLMS_FULL_TXT_PRESENT</t>
+        </is>
+      </c>
+      <c r="G340" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">L1, TP</t>
+        </is>
+      </c>
+      <c r="H340" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://llmstxt.org/</t>
+        </is>
+      </c>
+      <c r="I340" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Proposed — not adopted</t>
+        </is>
+      </c>
+      <c r="J340" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Tool policy</t>
+        </is>
+      </c>
+      <c r="K340" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Advisory. The file is published. No search engine consumes it, so this records a fact rather than a requirement met. The 20-word substantiveness floor is tool policy.</t>
+        </is>
+      </c>
+    </row>
+    <row r="341" ht="15.75" customHeight="1">
+      <c r="A341" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">X-5.3b</t>
+        </is>
+      </c>
+      <c r="B341" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">X-5.3b-b</t>
+        </is>
+      </c>
+      <c r="C341" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">/llms-full.txt returns 404 or 410</t>
+        </is>
+      </c>
+      <c r="D341" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PASS</t>
+        </is>
+      </c>
+      <c r="E341" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">—</t>
+        </is>
+      </c>
+      <c r="F341" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LLMS_FULL_TXT_ABSENT</t>
+        </is>
+      </c>
+      <c r="G341" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">L1, TP</t>
+        </is>
+      </c>
+      <c r="H341" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://llmstxt.org/</t>
+        </is>
+      </c>
+      <c r="I341" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Proposed — not adopted</t>
+        </is>
+      </c>
+      <c r="J341" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Tool policy</t>
+        </is>
+      </c>
+      <c r="K341" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Advisory. Absence is not a defect: nothing requires this file. A clean 404 is the correct answer for a site that does not publish one.</t>
+        </is>
+      </c>
+    </row>
+    <row r="342" ht="15.75" customHeight="1">
+      <c r="A342" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">X-5.3b</t>
+        </is>
+      </c>
+      <c r="B342" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">X-5.3b-c</t>
+        </is>
+      </c>
+      <c r="C342" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">/llms-full.txt returns 200 with HTML, or with almost no content</t>
+        </is>
+      </c>
+      <c r="D342" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PASS</t>
+        </is>
+      </c>
+      <c r="E342" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">—</t>
+        </is>
+      </c>
+      <c r="F342" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LLMS_FULL_TXT_FALLBACK</t>
+        </is>
+      </c>
+      <c r="G342" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">L1, TP</t>
+        </is>
+      </c>
+      <c r="H342" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://llmstxt.org/</t>
+        </is>
+      </c>
+      <c r="I342" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Proposed — not adopted</t>
+        </is>
+      </c>
+      <c r="J342" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Tool policy</t>
+        </is>
+      </c>
+      <c r="K342" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Advisory. The server answered with a page instead of saying the file is absent, so no llms-full.txt is published. Distinguished from a real file so the two are not confused.</t>
+        </is>
+      </c>
+    </row>
+    <row r="343" ht="15.75" customHeight="1">
+      <c r="A343" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">X-5.3b</t>
+        </is>
+      </c>
+      <c r="B343" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">X-5.3b-d</t>
+        </is>
+      </c>
+      <c r="C343" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">The request did not resolve: no response, 403, 429, 5xx, or a bot challenge</t>
+        </is>
+      </c>
+      <c r="D343" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NOT_TESTABLE</t>
+        </is>
+      </c>
+      <c r="E343" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">—</t>
+        </is>
+      </c>
+      <c r="F343" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LLMS_FULL_TXT_FETCH_FAILED</t>
+        </is>
+      </c>
+      <c r="G343" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">L1, TP</t>
+        </is>
+      </c>
+      <c r="H343" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://llmstxt.org/</t>
+        </is>
+      </c>
+      <c r="I343" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Proposed — not adopted</t>
+        </is>
+      </c>
+      <c r="J343" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Tool policy</t>
+        </is>
+      </c>
+      <c r="K343" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Advisory. A request that did not resolve says nothing about whether the file exists.</t>
+        </is>
+      </c>
+    </row>
+    <row r="344" ht="15.75" customHeight="1">
+      <c r="A344" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">X-5.5</t>
+        </is>
+      </c>
+      <c r="B344" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">X-5.5-a</t>
+        </is>
+      </c>
+      <c r="C344" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">The registrable domain appears in the latest Common Crawl index</t>
+        </is>
+      </c>
+      <c r="D344" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PASS</t>
+        </is>
+      </c>
+      <c r="E344" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">—</t>
+        </is>
+      </c>
+      <c r="F344" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">COMMON_CRAWL_PRESENT</t>
+        </is>
+      </c>
+      <c r="G344" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CC, TP</t>
+        </is>
+      </c>
+      <c r="H344" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://commoncrawl.org/</t>
+        </is>
+      </c>
+      <c r="I344" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Third-party archive — not a search index</t>
+        </is>
+      </c>
+      <c r="J344" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Tool policy</t>
+        </is>
+      </c>
+      <c r="K344" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Advisory. Confirms a URL from the domain was captured in that crawl, and nothing further: not training, not citation, not search visibility, not current crawler access.</t>
+        </is>
+      </c>
+    </row>
+    <row r="345" ht="15.75" customHeight="1">
+      <c r="A345" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">X-5.5</t>
+        </is>
+      </c>
+      <c r="B345" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">X-5.5-b</t>
+        </is>
+      </c>
+      <c r="C345" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Not in the latest index, but present in one of the previous two releases</t>
+        </is>
+      </c>
+      <c r="D345" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PASS</t>
+        </is>
+      </c>
+      <c r="E345" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">—</t>
+        </is>
+      </c>
+      <c r="F345" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">COMMON_CRAWL_PRESENT_RECENTLY</t>
+        </is>
+      </c>
+      <c r="G345" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CC, TP</t>
+        </is>
+      </c>
+      <c r="H345" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://commoncrawl.org/</t>
+        </is>
+      </c>
+      <c r="I345" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Third-party archive — not a search index</t>
+        </is>
+      </c>
+      <c r="J345" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Tool policy</t>
+        </is>
+      </c>
+      <c r="K345" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Advisory. Coverage varies between releases, so absence from the newest one is not evidence of a change on the site. Checking three releases rather than the whole archive is tool policy, to keep an initial audit fast.</t>
+        </is>
+      </c>
+    </row>
+    <row r="346" ht="15.75" customHeight="1">
+      <c r="A346" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">X-5.5</t>
+        </is>
+      </c>
+      <c r="B346" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">X-5.5-c</t>
+        </is>
+      </c>
+      <c r="C346" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">No capture in the latest three Common Crawl releases</t>
+        </is>
+      </c>
+      <c r="D346" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PASS</t>
+        </is>
+      </c>
+      <c r="E346" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">—</t>
+        </is>
+      </c>
+      <c r="F346" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">COMMON_CRAWL_NOT_FOUND_RECENT</t>
+        </is>
+      </c>
+      <c r="G346" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CC, TP</t>
+        </is>
+      </c>
+      <c r="H346" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://commoncrawl.org/</t>
+        </is>
+      </c>
+      <c r="I346" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Third-party archive — not a search index</t>
+        </is>
+      </c>
+      <c r="J346" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Tool policy</t>
+        </is>
+      </c>
+      <c r="K346" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Advisory, and never a failure. Common Crawl samples the web rather than covering it, so absence is not evidence that a site is unreachable, unindexed or invisible to assistants.</t>
+        </is>
+      </c>
+    </row>
+    <row r="347" ht="15.75" customHeight="1">
+      <c r="A347" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">X-5.5</t>
+        </is>
+      </c>
+      <c r="B347" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">X-5.5-d</t>
+        </is>
+      </c>
+      <c r="C347" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">The Common Crawl index did not answer: 429, 5xx, timeout, network failure, or invalid JSON</t>
+        </is>
+      </c>
+      <c r="D347" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NOT_TESTABLE</t>
+        </is>
+      </c>
+      <c r="E347" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">—</t>
+        </is>
+      </c>
+      <c r="F347" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">COMMON_CRAWL_API_UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="G347" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CC, TP</t>
+        </is>
+      </c>
+      <c r="H347" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://commoncrawl.org/</t>
+        </is>
+      </c>
+      <c r="I347" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Third-party archive — not a search index</t>
+        </is>
+      </c>
+      <c r="J347" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Tool policy</t>
+        </is>
+      </c>
+      <c r="K347" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Advisory. The CDX API answers 503/504 under load often enough that one retry with backoff is built in. An API that still did not answer says nothing about the domain, and must not be reported as absence.</t>
         </is>
       </c>
     </row>
